--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261013.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261013.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>16,273,000</t>
+          <t>56,668,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>56,668,000</t>
+          <t>16,273,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>17,752,000</t>
+          <t>16,031,073</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>16,031,073</t>
+          <t>17,752,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
